--- a/portal.solexpress/public/static/etower-create-sample.xlsx
+++ b/portal.solexpress/public/static/etower-create-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
   <si>
     <t>Ref No.</t>
   </si>
@@ -70,9 +70,21 @@
     <t>Shipper Facility/Origin</t>
   </si>
   <si>
+    <t>Return Country</t>
+  </si>
+  <si>
     <t>Return Name</t>
   </si>
   <si>
+    <t>Return State</t>
+  </si>
+  <si>
+    <t>Return Phone</t>
+  </si>
+  <si>
+    <t>Return Postcode</t>
+  </si>
+  <si>
     <t>Shipper Company Name</t>
   </si>
   <si>
@@ -82,6 +94,33 @@
     <t>Shipper Name</t>
   </si>
   <si>
+    <t>Service Option</t>
+  </si>
+  <si>
+    <t>Shipper Organization Code</t>
+  </si>
+  <si>
+    <t>Shipper Email</t>
+  </si>
+  <si>
+    <t>Shipper Postcode</t>
+  </si>
+  <si>
+    <t>Shipper State</t>
+  </si>
+  <si>
+    <t>Shipper City</t>
+  </si>
+  <si>
+    <t>Shipper Address Line 1</t>
+  </si>
+  <si>
+    <t>Shipper Phone</t>
+  </si>
+  <si>
+    <t>Shipper Country</t>
+  </si>
+  <si>
     <t>referenceNo</t>
   </si>
   <si>
@@ -142,12 +181,51 @@
     <t>returnCountry</t>
   </si>
   <si>
+    <t>returnName</t>
+  </si>
+  <si>
+    <t>returnState</t>
+  </si>
+  <si>
+    <t>returnPhone</t>
+  </si>
+  <si>
+    <t>returnPostcode</t>
+  </si>
+  <si>
     <t>shipperCompanyName</t>
   </si>
   <si>
     <t>shipperName</t>
   </si>
   <si>
+    <t>serviceOption</t>
+  </si>
+  <si>
+    <t>shipperOrganizationCode</t>
+  </si>
+  <si>
+    <t>shipperEmail</t>
+  </si>
+  <si>
+    <t>shipperPostcode</t>
+  </si>
+  <si>
+    <t>shipperState</t>
+  </si>
+  <si>
+    <t>shipperCity</t>
+  </si>
+  <si>
+    <t>shipperAddressLine1</t>
+  </si>
+  <si>
+    <t>shipperPhone</t>
+  </si>
+  <si>
+    <t>shipperCountry</t>
+  </si>
+  <si>
     <t>2222199236410011111</t>
   </si>
   <si>
@@ -185,6 +263,9 @@
   </si>
   <si>
     <t>UBI.AU2AU.AUPOST.Y</t>
+  </si>
+  <si>
+    <t>E-Parcel</t>
   </si>
 </sst>
 </file>
@@ -194,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -206,12 +287,6 @@
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -229,6 +304,25 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color theme="5"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFEA4335"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -236,15 +330,10 @@
     <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
       <name val="PMingLiu"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,12 +344,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -296,36 +379,42 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -565,12 +654,18 @@
     <col customWidth="1" min="17" max="17" width="6.75"/>
     <col customWidth="1" min="18" max="18" width="7.38"/>
     <col customWidth="1" min="19" max="19" width="22.88"/>
-    <col customWidth="1" min="20" max="20" width="14.13"/>
-    <col customWidth="1" min="21" max="22" width="24.63"/>
-    <col customWidth="1" min="23" max="23" width="14.75"/>
-    <col customWidth="1" min="25" max="26" width="20.63"/>
-    <col customWidth="1" min="27" max="27" width="21.0"/>
-    <col customWidth="1" min="28" max="28" width="35.13"/>
+    <col customWidth="1" min="20" max="20" width="14.88"/>
+    <col customWidth="1" min="21" max="26" width="24.63"/>
+    <col customWidth="1" min="27" max="27" width="14.75"/>
+    <col customWidth="1" min="28" max="28" width="13.75"/>
+    <col customWidth="1" min="29" max="29" width="24.5"/>
+    <col customWidth="1" min="30" max="30" width="20.63"/>
+    <col customWidth="1" min="31" max="31" width="21.0"/>
+    <col customWidth="1" min="32" max="32" width="35.13"/>
+    <col customWidth="1" min="33" max="33" width="12.0"/>
+    <col customWidth="1" min="34" max="34" width="21.13"/>
+    <col customWidth="1" min="35" max="35" width="13.63"/>
+    <col customWidth="1" min="36" max="36" width="15.5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -631,27 +726,57 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AK1" s="3"/>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
@@ -659,120 +784,163 @@
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
     </row>
     <row r="2" ht="15.75" hidden="1" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>44</v>
+      <c r="AA2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>47</v>
+      <c r="A3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="G3" s="8">
         <v>4077.0</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="I3" s="8">
         <v>6.140655734E10</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="K3" s="10">
         <v>120.0</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="M3" s="8">
         <v>11.0</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="P3" s="8">
         <v>60.0</v>
@@ -784,19 +952,28 @@
         <v>19.0</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>56</v>
+        <v>82</v>
+      </c>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -821,8 +998,12 @@
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
-      <c r="V4" s="4"/>
+      <c r="V4" s="9"/>
       <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="9"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
@@ -846,8 +1027,12 @@
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="4"/>
+      <c r="V5" s="9"/>
       <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="9"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
@@ -871,8 +1056,12 @@
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="4"/>
+      <c r="V6" s="9"/>
       <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="9"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
@@ -896,8 +1085,12 @@
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="4"/>
+      <c r="V7" s="9"/>
       <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="9"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
@@ -921,8 +1114,12 @@
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="V8" s="4"/>
+      <c r="V8" s="9"/>
       <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="9"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
@@ -946,8 +1143,12 @@
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="V9" s="4"/>
+      <c r="V9" s="9"/>
       <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
@@ -971,8 +1172,12 @@
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="V10" s="4"/>
+      <c r="V10" s="9"/>
       <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="9"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
@@ -996,8 +1201,12 @@
       <c r="S11" s="9"/>
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
-      <c r="V11" s="4"/>
+      <c r="V11" s="9"/>
       <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="9"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
@@ -1021,8 +1230,12 @@
       <c r="S12" s="9"/>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
-      <c r="V12" s="4"/>
+      <c r="V12" s="9"/>
       <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="9"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
@@ -1046,8 +1259,12 @@
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
-      <c r="V13" s="4"/>
+      <c r="V13" s="9"/>
       <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="9"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
@@ -1071,8 +1288,12 @@
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
-      <c r="V14" s="4"/>
+      <c r="V14" s="9"/>
       <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="9"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
@@ -1096,8 +1317,12 @@
       <c r="S15" s="9"/>
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
-      <c r="V15" s="4"/>
+      <c r="V15" s="9"/>
       <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
@@ -1121,8 +1346,12 @@
       <c r="S16" s="9"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
-      <c r="V16" s="4"/>
+      <c r="V16" s="9"/>
       <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
@@ -1146,8 +1375,12 @@
       <c r="S17" s="9"/>
       <c r="T17" s="9"/>
       <c r="U17" s="9"/>
-      <c r="V17" s="4"/>
+      <c r="V17" s="9"/>
       <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
@@ -1171,8 +1404,12 @@
       <c r="S18" s="9"/>
       <c r="T18" s="9"/>
       <c r="U18" s="9"/>
-      <c r="V18" s="4"/>
+      <c r="V18" s="9"/>
       <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="9"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
@@ -1196,8 +1433,12 @@
       <c r="S19" s="9"/>
       <c r="T19" s="9"/>
       <c r="U19" s="9"/>
-      <c r="V19" s="4"/>
+      <c r="V19" s="9"/>
       <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
@@ -1221,8 +1462,12 @@
       <c r="S20" s="9"/>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
-      <c r="V20" s="4"/>
+      <c r="V20" s="9"/>
       <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
@@ -1246,8 +1491,12 @@
       <c r="S21" s="9"/>
       <c r="T21" s="9"/>
       <c r="U21" s="9"/>
-      <c r="V21" s="4"/>
+      <c r="V21" s="9"/>
       <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
@@ -1271,8 +1520,12 @@
       <c r="S22" s="9"/>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
-      <c r="V22" s="4"/>
+      <c r="V22" s="9"/>
       <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
@@ -1296,8 +1549,12 @@
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
-      <c r="V23" s="4"/>
+      <c r="V23" s="9"/>
       <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
@@ -1321,8 +1578,12 @@
       <c r="S24" s="9"/>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
-      <c r="V24" s="4"/>
+      <c r="V24" s="9"/>
       <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
@@ -1346,8 +1607,12 @@
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
-      <c r="V25" s="4"/>
+      <c r="V25" s="9"/>
       <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
@@ -1362,7 +1627,7 @@
       <c r="J26" s="9"/>
       <c r="K26" s="10"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="11"/>
+      <c r="M26" s="13"/>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
       <c r="P26" s="10"/>
@@ -1371,8 +1636,12 @@
       <c r="S26" s="9"/>
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
-      <c r="V26" s="4"/>
+      <c r="V26" s="9"/>
       <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
@@ -1396,8 +1665,12 @@
       <c r="S27" s="9"/>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
-      <c r="V27" s="4"/>
+      <c r="V27" s="9"/>
       <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -1421,8 +1694,12 @@
       <c r="S28" s="9"/>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
-      <c r="V28" s="4"/>
+      <c r="V28" s="9"/>
       <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
@@ -1446,8 +1723,12 @@
       <c r="S29" s="9"/>
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
-      <c r="V29" s="4"/>
+      <c r="V29" s="9"/>
       <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
@@ -1471,8 +1752,12 @@
       <c r="S30" s="9"/>
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
-      <c r="V30" s="4"/>
+      <c r="V30" s="9"/>
       <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
@@ -1496,11 +1781,15 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
-      <c r="V31" s="4"/>
+      <c r="V31" s="9"/>
       <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="S32" s="12"/>
+      <c r="S32" s="14"/>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -2468,6 +2757,8 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/portal.solexpress/public/static/etower-create-sample.xlsx
+++ b/portal.solexpress/public/static/etower-create-sample.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>Ref No.</t>
   </si>
   <si>
+    <t>serviceCode</t>
+  </si>
+  <si>
     <t>Recipient Name</t>
   </si>
   <si>
@@ -76,51 +79,15 @@
     <t>Return Name</t>
   </si>
   <si>
-    <t>Return State</t>
-  </si>
-  <si>
-    <t>Return Phone</t>
-  </si>
-  <si>
-    <t>Return Postcode</t>
-  </si>
-  <si>
     <t>Shipper Company Name</t>
   </si>
   <si>
-    <t>serviceCode</t>
-  </si>
-  <si>
     <t>Shipper Name</t>
   </si>
   <si>
     <t>Service Option</t>
   </si>
   <si>
-    <t>Shipper Organization Code</t>
-  </si>
-  <si>
-    <t>Shipper Email</t>
-  </si>
-  <si>
-    <t>Shipper Postcode</t>
-  </si>
-  <si>
-    <t>Shipper State</t>
-  </si>
-  <si>
-    <t>Shipper City</t>
-  </si>
-  <si>
-    <t>Shipper Address Line 1</t>
-  </si>
-  <si>
-    <t>Shipper Phone</t>
-  </si>
-  <si>
-    <t>Shipper Country</t>
-  </si>
-  <si>
     <t>referenceNo</t>
   </si>
   <si>
@@ -184,15 +151,6 @@
     <t>returnName</t>
   </si>
   <si>
-    <t>returnState</t>
-  </si>
-  <si>
-    <t>returnPhone</t>
-  </si>
-  <si>
-    <t>returnPostcode</t>
-  </si>
-  <si>
     <t>shipperCompanyName</t>
   </si>
   <si>
@@ -202,31 +160,10 @@
     <t>serviceOption</t>
   </si>
   <si>
-    <t>shipperOrganizationCode</t>
-  </si>
-  <si>
-    <t>shipperEmail</t>
-  </si>
-  <si>
-    <t>shipperPostcode</t>
-  </si>
-  <si>
-    <t>shipperState</t>
-  </si>
-  <si>
-    <t>shipperCity</t>
-  </si>
-  <si>
-    <t>shipperAddressLine1</t>
-  </si>
-  <si>
-    <t>shipperPhone</t>
-  </si>
-  <si>
-    <t>shipperCountry</t>
-  </si>
-  <si>
-    <t>2222199236410011111</t>
+    <t>32222199236410011111</t>
+  </si>
+  <si>
+    <t>UBI.AU2AU.AUPOST.Y</t>
   </si>
   <si>
     <t>TEST</t>
@@ -259,13 +196,10 @@
     <t>MEL</t>
   </si>
   <si>
+    <t>MINH QUANG</t>
+  </si>
+  <si>
     <t>SLINT</t>
-  </si>
-  <si>
-    <t>UBI.AU2AU.AUPOST.Y</t>
-  </si>
-  <si>
-    <t>E-Parcel</t>
   </si>
 </sst>
 </file>
@@ -275,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -300,17 +234,12 @@
     </font>
     <font>
       <sz val="12.0"/>
-      <color rgb="FF172B4D"/>
+      <color rgb="FFEA4335"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12.0"/>
-      <color theme="5"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FFEA4335"/>
+      <color rgb="FF172B4D"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -392,29 +321,29 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -636,39 +565,33 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="11.25"/>
-    <col customWidth="1" min="2" max="2" width="33.0"/>
-    <col customWidth="1" min="3" max="3" width="28.25"/>
-    <col customWidth="1" min="4" max="4" width="14.75"/>
-    <col customWidth="1" min="5" max="5" width="22.75"/>
-    <col customWidth="1" min="6" max="6" width="6.13"/>
-    <col customWidth="1" min="7" max="7" width="9.63"/>
-    <col customWidth="1" min="8" max="8" width="8.75"/>
-    <col customWidth="1" min="9" max="9" width="13.75"/>
-    <col customWidth="1" min="10" max="10" width="17.75"/>
-    <col customWidth="1" min="11" max="11" width="14.25"/>
-    <col customWidth="1" min="12" max="12" width="27.63"/>
-    <col customWidth="1" min="13" max="13" width="12.75"/>
-    <col customWidth="1" min="14" max="14" width="18.25"/>
-    <col customWidth="1" min="15" max="15" width="15.88"/>
-    <col customWidth="1" min="16" max="16" width="7.75"/>
-    <col customWidth="1" min="17" max="17" width="6.75"/>
-    <col customWidth="1" min="18" max="18" width="7.38"/>
-    <col customWidth="1" min="19" max="19" width="22.88"/>
-    <col customWidth="1" min="20" max="20" width="14.88"/>
-    <col customWidth="1" min="21" max="26" width="24.63"/>
-    <col customWidth="1" min="27" max="27" width="14.75"/>
-    <col customWidth="1" min="28" max="28" width="13.75"/>
-    <col customWidth="1" min="29" max="29" width="24.5"/>
-    <col customWidth="1" min="30" max="30" width="20.63"/>
-    <col customWidth="1" min="31" max="31" width="21.0"/>
-    <col customWidth="1" min="32" max="32" width="35.13"/>
-    <col customWidth="1" min="33" max="33" width="12.0"/>
-    <col customWidth="1" min="34" max="34" width="21.13"/>
-    <col customWidth="1" min="35" max="35" width="13.63"/>
-    <col customWidth="1" min="36" max="36" width="15.5"/>
+    <col customWidth="1" min="2" max="2" width="24.63"/>
+    <col customWidth="1" min="3" max="3" width="33.0"/>
+    <col customWidth="1" min="4" max="4" width="28.25"/>
+    <col customWidth="1" min="5" max="5" width="14.75"/>
+    <col customWidth="1" min="6" max="6" width="22.75"/>
+    <col customWidth="1" min="7" max="7" width="6.13"/>
+    <col customWidth="1" min="8" max="8" width="9.63"/>
+    <col customWidth="1" min="9" max="9" width="8.75"/>
+    <col customWidth="1" min="10" max="10" width="13.75"/>
+    <col customWidth="1" min="11" max="11" width="17.75"/>
+    <col customWidth="1" min="12" max="12" width="14.25"/>
+    <col customWidth="1" min="13" max="13" width="27.63"/>
+    <col customWidth="1" min="14" max="14" width="12.75"/>
+    <col customWidth="1" min="15" max="15" width="18.25"/>
+    <col customWidth="1" min="16" max="16" width="15.88"/>
+    <col customWidth="1" min="17" max="17" width="7.75"/>
+    <col customWidth="1" min="18" max="18" width="6.75"/>
+    <col customWidth="1" min="19" max="19" width="7.38"/>
+    <col customWidth="1" min="20" max="20" width="22.88"/>
+    <col customWidth="1" min="21" max="21" width="14.88"/>
+    <col customWidth="1" min="22" max="23" width="24.63"/>
+    <col customWidth="1" min="25" max="27" width="24.63"/>
+    <col customWidth="1" min="28" max="28" width="14.75"/>
+    <col customWidth="1" min="29" max="29" width="13.75"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,255 +649,184 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3"/>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
-    </row>
-    <row r="2" ht="15.75" hidden="1" customHeight="1">
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="P2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="Q2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="R2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="S2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="T2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="U2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="V2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="W2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="X2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="Y2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="4" t="s">
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="C3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="F3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="G3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="H3" s="8">
+        <v>4077.0</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="J3" s="8">
+        <v>6.140655734E10</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="L3" s="10">
+        <v>120.0</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="N3" s="8">
+        <v>11.0</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="P3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Q3" s="8">
+        <v>60.0</v>
+      </c>
+      <c r="R3" s="8">
+        <v>31.0</v>
+      </c>
+      <c r="S3" s="8">
+        <v>19.0</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="Z2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="7" t="s">
+      <c r="U3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="W3" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="AC2" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ2" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="8">
-        <v>4077.0</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="8">
-        <v>6.140655734E10</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="10">
-        <v>120.0</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3" s="8">
-        <v>11.0</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="P3" s="8">
-        <v>60.0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>31.0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>19.0</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB3" s="12" t="s">
-        <v>84</v>
-      </c>
+      <c r="X3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="12"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
@@ -983,27 +835,27 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="10"/>
+      <c r="P4" s="9"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
-      <c r="S4" s="9"/>
+      <c r="S4" s="10"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="9"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
@@ -1012,27 +864,27 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
       <c r="O5" s="9"/>
-      <c r="P5" s="10"/>
+      <c r="P5" s="9"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
-      <c r="S5" s="9"/>
+      <c r="S5" s="10"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
       <c r="Y5" s="9"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="9"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
@@ -1041,27 +893,27 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="P6" s="9"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="9"/>
+      <c r="S6" s="10"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
       <c r="Y6" s="9"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="9"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
@@ -1070,27 +922,27 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
       <c r="O7" s="9"/>
-      <c r="P7" s="10"/>
+      <c r="P7" s="9"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
-      <c r="S7" s="9"/>
+      <c r="S7" s="10"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="9"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
@@ -1099,27 +951,27 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
+      <c r="P8" s="9"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
-      <c r="S8" s="9"/>
+      <c r="S8" s="10"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
       <c r="Y8" s="9"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="9"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
@@ -1128,27 +980,27 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="10"/>
+      <c r="P9" s="9"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="9"/>
+      <c r="S9" s="10"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
@@ -1157,27 +1009,27 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
+      <c r="P10" s="9"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
-      <c r="S10" s="9"/>
+      <c r="S10" s="10"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="9"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
@@ -1186,27 +1038,27 @@
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="10"/>
+      <c r="P11" s="9"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="10"/>
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="9"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
@@ -1215,27 +1067,27 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
+      <c r="P12" s="9"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="10"/>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="9"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
@@ -1244,27 +1096,27 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
       <c r="O13" s="9"/>
-      <c r="P13" s="10"/>
+      <c r="P13" s="9"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
-      <c r="S13" s="9"/>
+      <c r="S13" s="10"/>
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="9"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
@@ -1273,27 +1125,27 @@
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10"/>
       <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
+      <c r="P14" s="9"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
-      <c r="S14" s="9"/>
+      <c r="S14" s="10"/>
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
       <c r="Y14" s="9"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="9"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
@@ -1302,27 +1154,27 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="10"/>
+      <c r="P15" s="9"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
-      <c r="S15" s="9"/>
+      <c r="S15" s="10"/>
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
       <c r="Y15" s="9"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
@@ -1331,27 +1183,27 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
       <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
+      <c r="P16" s="9"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="9"/>
+      <c r="S16" s="10"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
@@ -1360,27 +1212,27 @@
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="10"/>
+      <c r="P17" s="9"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
-      <c r="S17" s="9"/>
+      <c r="S17" s="10"/>
       <c r="T17" s="9"/>
       <c r="U17" s="9"/>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
@@ -1389,27 +1241,27 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10"/>
       <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
+      <c r="P18" s="9"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
-      <c r="S18" s="9"/>
+      <c r="S18" s="10"/>
       <c r="T18" s="9"/>
       <c r="U18" s="9"/>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="9"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
@@ -1418,27 +1270,27 @@
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
       <c r="O19" s="9"/>
-      <c r="P19" s="10"/>
+      <c r="P19" s="9"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
-      <c r="S19" s="9"/>
+      <c r="S19" s="10"/>
       <c r="T19" s="9"/>
       <c r="U19" s="9"/>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="9"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
@@ -1447,27 +1299,27 @@
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="10"/>
       <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
+      <c r="P20" s="9"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
-      <c r="S20" s="9"/>
+      <c r="S20" s="10"/>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="9"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
@@ -1476,27 +1328,27 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10"/>
       <c r="O21" s="9"/>
-      <c r="P21" s="10"/>
+      <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
-      <c r="S21" s="9"/>
+      <c r="S21" s="10"/>
       <c r="T21" s="9"/>
       <c r="U21" s="9"/>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="9"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
@@ -1505,27 +1357,27 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
       <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
+      <c r="P22" s="9"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
-      <c r="S22" s="9"/>
+      <c r="S22" s="10"/>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
@@ -1534,27 +1386,27 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="10"/>
       <c r="O23" s="9"/>
-      <c r="P23" s="10"/>
+      <c r="P23" s="9"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
-      <c r="S23" s="9"/>
+      <c r="S23" s="10"/>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
@@ -1563,27 +1415,27 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="13"/>
       <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
+      <c r="P24" s="9"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
-      <c r="S24" s="9"/>
+      <c r="S24" s="10"/>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
@@ -1592,27 +1444,27 @@
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
       <c r="O25" s="9"/>
-      <c r="P25" s="10"/>
+      <c r="P25" s="9"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="10"/>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
@@ -1621,27 +1473,27 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
       <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
+      <c r="P26" s="9"/>
       <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
-      <c r="S26" s="9"/>
+      <c r="S26" s="10"/>
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
       <c r="Y26" s="9"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
@@ -1650,27 +1502,27 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
       <c r="O27" s="9"/>
-      <c r="P27" s="10"/>
+      <c r="P27" s="9"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
-      <c r="S27" s="9"/>
+      <c r="S27" s="10"/>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -1679,27 +1531,27 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
       <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
+      <c r="P28" s="9"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
-      <c r="S28" s="9"/>
+      <c r="S28" s="10"/>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
@@ -1708,89 +1560,33 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="10"/>
+      <c r="P29" s="9"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
-      <c r="S29" s="9"/>
+      <c r="S29" s="10"/>
       <c r="T29" s="9"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="9"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="S32" s="14"/>
-    </row>
+      <c r="T30" s="14"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2757,8 +2553,6 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
